--- a/backend/测试数据/计算机网络成绩汇总测试数据.xlsx
+++ b/backend/测试数据/计算机网络成绩汇总测试数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21750" windowHeight="12040" activeTab="1"/>
+    <workbookView windowWidth="21750" windowHeight="12040" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="软件1801" sheetId="5" r:id="rId1"/>
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">软件1803!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">软件1802!$A$1:$D$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">软件1802!$A$1:$E$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,9 +33,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="154">
   <si>
     <t>编号</t>
+  </si>
+  <si>
+    <t>课程号</t>
   </si>
   <si>
     <t>课程名称</t>
@@ -1601,22 +1604,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="11.4363636363636" customWidth="1"/>
-    <col min="3" max="3" width="14.2727272727273" customWidth="1"/>
-    <col min="4" max="4" width="11.4363636363636" customWidth="1"/>
-    <col min="5" max="5" width="13.7272727272727" customWidth="1"/>
-    <col min="7" max="7" width="12.3636363636364" customWidth="1"/>
-    <col min="8" max="8" width="12.7545454545455" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10.8727272727273" customWidth="1"/>
-    <col min="14" max="14" width="12.8181818181818" style="17"/>
-    <col min="15" max="15" width="12.8181818181818" style="18"/>
+    <col min="2" max="3" width="11.4363636363636" customWidth="1"/>
+    <col min="4" max="4" width="14.2727272727273" customWidth="1"/>
+    <col min="5" max="5" width="11.4363636363636" customWidth="1"/>
+    <col min="6" max="6" width="13.7272727272727" customWidth="1"/>
+    <col min="8" max="8" width="12.3636363636364" customWidth="1"/>
+    <col min="9" max="9" width="12.7545454545455" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="12" max="12" width="10.8727272727273" customWidth="1"/>
+    <col min="15" max="15" width="12.8181818181818" style="17"/>
+    <col min="16" max="16" width="12.8181818181818" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1632,16 +1635,16 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
@@ -1656,1259 +1659,1337 @@
       <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+      <c r="P1" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="22" t="s">
+      <c r="B2" s="20">
+        <v>1</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="21" t="s">
         <v>17</v>
       </c>
       <c r="E2" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="19">
         <v>88</v>
       </c>
-      <c r="G2" s="19">
+      <c r="H2" s="19">
         <v>65</v>
       </c>
-      <c r="H2" s="19">
+      <c r="I2" s="19">
         <v>72</v>
       </c>
-      <c r="I2" s="19">
-        <f>ROUND(AVERAGE(F2:H2),0)</f>
+      <c r="J2" s="19">
+        <f>ROUND(AVERAGE(G2:I2),0)</f>
         <v>75</v>
       </c>
-      <c r="J2" s="19">
+      <c r="K2" s="19">
         <v>60</v>
       </c>
-      <c r="K2" s="19">
+      <c r="L2" s="19">
         <v>0</v>
       </c>
-      <c r="L2" s="19">
+      <c r="M2" s="19">
         <v>67</v>
       </c>
-      <c r="M2" s="19">
-        <f>ROUND(AVERAGE(J2:L2),0)</f>
+      <c r="N2" s="19">
+        <f>ROUND(AVERAGE(K2:M2),0)</f>
         <v>42</v>
       </c>
-      <c r="N2" s="23">
+      <c r="O2" s="23">
         <v>95</v>
       </c>
-      <c r="O2" s="24">
-        <f>0.25*I2+0.25*M2+0.5*N2</f>
+      <c r="P2" s="24">
+        <f>0.25*J2+0.25*N2+0.5*O2</f>
         <v>76.75</v>
       </c>
     </row>
-    <row r="3" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="3" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>19</v>
+      <c r="B3" s="20">
+        <v>1</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E3" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="19">
         <v>83</v>
-      </c>
-      <c r="G3" s="19">
-        <v>96</v>
       </c>
       <c r="H3" s="19">
         <v>96</v>
       </c>
       <c r="I3" s="19">
-        <f t="shared" ref="I3:I26" si="0">ROUND(AVERAGE(F3:H3),0)</f>
+        <v>96</v>
+      </c>
+      <c r="J3" s="19">
+        <f t="shared" ref="J3:J26" si="0">ROUND(AVERAGE(G3:I3),0)</f>
         <v>92</v>
       </c>
-      <c r="J3" s="19">
+      <c r="K3" s="19">
         <v>80</v>
-      </c>
-      <c r="K3" s="19">
-        <v>84</v>
       </c>
       <c r="L3" s="19">
         <v>84</v>
       </c>
       <c r="M3" s="19">
-        <f t="shared" ref="M3:M26" si="1">ROUND(AVERAGE(J3:L3),0)</f>
+        <v>84</v>
+      </c>
+      <c r="N3" s="19">
+        <f t="shared" ref="N3:N26" si="1">ROUND(AVERAGE(K3:M3),0)</f>
         <v>83</v>
       </c>
-      <c r="N3" s="23">
-        <v>90</v>
-      </c>
-      <c r="O3" s="24">
-        <f t="shared" ref="O3:O26" si="2">0.25*I3+0.25*M3+0.5*N3</f>
+      <c r="O3" s="23">
+        <v>90</v>
+      </c>
+      <c r="P3" s="24">
+        <f t="shared" ref="P3:P26" si="2">0.25*J3+0.25*N3+0.5*O3</f>
         <v>88.75</v>
       </c>
     </row>
-    <row r="4" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="4" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>21</v>
+      <c r="B4" s="20">
+        <v>1</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="19">
         <v>87</v>
       </c>
-      <c r="G4" s="19">
+      <c r="H4" s="19">
         <v>89</v>
       </c>
-      <c r="H4" s="19">
+      <c r="I4" s="19">
         <v>94</v>
       </c>
-      <c r="I4" s="19">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
       <c r="J4" s="19">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="K4" s="19">
         <v>95</v>
       </c>
-      <c r="K4" s="19">
+      <c r="L4" s="19">
         <v>92</v>
       </c>
-      <c r="L4" s="19">
-        <v>90</v>
-      </c>
       <c r="M4" s="19">
+        <v>90</v>
+      </c>
+      <c r="N4" s="19">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
-      <c r="N4" s="23">
+      <c r="O4" s="23">
         <v>85</v>
       </c>
-      <c r="O4" s="24">
+      <c r="P4" s="24">
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
     </row>
-    <row r="5" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="5" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A5" s="19">
         <v>4</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>23</v>
+      <c r="B5" s="20">
+        <v>1</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E5" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="19">
         <v>76</v>
       </c>
-      <c r="G5" s="19">
+      <c r="H5" s="19">
         <v>85</v>
       </c>
-      <c r="H5" s="19">
-        <v>90</v>
-      </c>
       <c r="I5" s="19">
+        <v>90</v>
+      </c>
+      <c r="J5" s="19">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="J5" s="19">
-        <v>90</v>
-      </c>
       <c r="K5" s="19">
+        <v>90</v>
+      </c>
+      <c r="L5" s="19">
         <v>88</v>
       </c>
-      <c r="L5" s="19">
+      <c r="M5" s="19">
         <v>85</v>
       </c>
-      <c r="M5" s="19">
+      <c r="N5" s="19">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="N5" s="23">
+      <c r="O5" s="23">
         <v>84</v>
       </c>
-      <c r="O5" s="24">
+      <c r="P5" s="24">
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
     </row>
-    <row r="6" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="6" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>25</v>
+      <c r="B6" s="20">
+        <v>1</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E6" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="19">
         <v>89</v>
       </c>
-      <c r="G6" s="19">
+      <c r="H6" s="19">
         <v>87</v>
       </c>
-      <c r="H6" s="19">
+      <c r="I6" s="19">
         <v>91</v>
       </c>
-      <c r="I6" s="19">
+      <c r="J6" s="19">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="J6" s="19">
+      <c r="K6" s="19">
         <v>93</v>
       </c>
-      <c r="K6" s="19">
+      <c r="L6" s="19">
         <v>87</v>
       </c>
-      <c r="L6" s="19">
+      <c r="M6" s="19">
         <v>78</v>
       </c>
-      <c r="M6" s="19">
+      <c r="N6" s="19">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
-      <c r="N6" s="23">
+      <c r="O6" s="23">
         <v>80</v>
       </c>
-      <c r="O6" s="24">
+      <c r="P6" s="24">
         <f t="shared" si="2"/>
         <v>83.75</v>
       </c>
     </row>
-    <row r="7" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="7" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="22" t="s">
+      <c r="B7" s="20">
+        <v>1</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="19">
         <v>85</v>
       </c>
-      <c r="G7" s="19">
+      <c r="H7" s="19">
         <v>88</v>
       </c>
-      <c r="H7" s="19">
+      <c r="I7" s="19">
         <v>92</v>
       </c>
-      <c r="I7" s="19">
+      <c r="J7" s="19">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="J7" s="19">
+      <c r="K7" s="19">
         <v>93</v>
       </c>
-      <c r="K7" s="19">
-        <v>90</v>
-      </c>
       <c r="L7" s="19">
+        <v>90</v>
+      </c>
+      <c r="M7" s="19">
         <v>78</v>
       </c>
-      <c r="M7" s="19">
+      <c r="N7" s="19">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="N7" s="23">
+      <c r="O7" s="23">
         <v>68</v>
       </c>
-      <c r="O7" s="24">
+      <c r="P7" s="24">
         <f t="shared" si="2"/>
         <v>77.75</v>
       </c>
     </row>
-    <row r="8" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="8" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A8" s="19">
         <v>7</v>
       </c>
-      <c r="B8" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>29</v>
+      <c r="B8" s="20">
+        <v>1</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E8" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="19">
         <v>89</v>
       </c>
-      <c r="G8" s="19">
+      <c r="H8" s="19">
         <v>78</v>
       </c>
-      <c r="H8" s="19">
+      <c r="I8" s="19">
         <v>92</v>
       </c>
-      <c r="I8" s="19">
+      <c r="J8" s="19">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
-      <c r="J8" s="19">
+      <c r="K8" s="19">
         <v>85</v>
       </c>
-      <c r="K8" s="19">
+      <c r="L8" s="19">
         <v>84</v>
       </c>
-      <c r="L8" s="19">
+      <c r="M8" s="19">
         <v>78</v>
       </c>
-      <c r="M8" s="19">
+      <c r="N8" s="19">
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
-      <c r="N8" s="23">
+      <c r="O8" s="23">
         <v>85</v>
       </c>
-      <c r="O8" s="24">
+      <c r="P8" s="24">
         <f t="shared" si="2"/>
         <v>84.5</v>
       </c>
     </row>
-    <row r="9" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="9" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>31</v>
+      <c r="B9" s="20">
+        <v>1</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E9" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="19">
         <v>87</v>
       </c>
-      <c r="G9" s="19">
+      <c r="H9" s="19">
         <v>98</v>
       </c>
-      <c r="H9" s="19">
+      <c r="I9" s="19">
         <v>97</v>
       </c>
-      <c r="I9" s="19">
+      <c r="J9" s="19">
         <f t="shared" si="0"/>
         <v>94</v>
-      </c>
-      <c r="J9" s="19">
-        <v>93</v>
       </c>
       <c r="K9" s="19">
         <v>93</v>
       </c>
       <c r="L9" s="19">
+        <v>93</v>
+      </c>
+      <c r="M9" s="19">
         <v>79</v>
       </c>
-      <c r="M9" s="19">
+      <c r="N9" s="19">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="N9" s="23">
+      <c r="O9" s="23">
         <v>61</v>
       </c>
-      <c r="O9" s="24">
+      <c r="P9" s="24">
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
     </row>
-    <row r="10" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="10" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A10" s="19">
         <v>9</v>
       </c>
-      <c r="B10" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>33</v>
+      <c r="B10" s="20">
+        <v>1</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E10" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="19">
         <v>93</v>
-      </c>
-      <c r="G10" s="19">
-        <v>94</v>
       </c>
       <c r="H10" s="19">
         <v>94</v>
       </c>
       <c r="I10" s="19">
-        <f t="shared" si="0"/>
         <v>94</v>
       </c>
       <c r="J10" s="19">
+        <f t="shared" si="0"/>
+        <v>94</v>
+      </c>
+      <c r="K10" s="19">
         <v>95</v>
       </c>
-      <c r="K10" s="19">
+      <c r="L10" s="19">
         <v>92</v>
       </c>
-      <c r="L10" s="19">
+      <c r="M10" s="19">
         <v>91</v>
       </c>
-      <c r="M10" s="19">
+      <c r="N10" s="19">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
-      <c r="N10" s="23">
+      <c r="O10" s="23">
         <v>79</v>
       </c>
-      <c r="O10" s="24">
+      <c r="P10" s="24">
         <f t="shared" si="2"/>
         <v>86.25</v>
       </c>
     </row>
-    <row r="11" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="11" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A11" s="19">
         <v>10</v>
       </c>
-      <c r="B11" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>35</v>
+      <c r="B11" s="20">
+        <v>1</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E11" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="19">
         <v>83</v>
       </c>
-      <c r="G11" s="19">
+      <c r="H11" s="19">
         <v>88</v>
       </c>
-      <c r="H11" s="19">
+      <c r="I11" s="19">
         <v>96</v>
       </c>
-      <c r="I11" s="19">
+      <c r="J11" s="19">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="J11" s="19">
-        <v>90</v>
-      </c>
       <c r="K11" s="19">
+        <v>90</v>
+      </c>
+      <c r="L11" s="19">
         <v>85</v>
       </c>
-      <c r="L11" s="19">
+      <c r="M11" s="19">
         <v>86</v>
       </c>
-      <c r="M11" s="19">
+      <c r="N11" s="19">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="N11" s="23">
+      <c r="O11" s="23">
         <v>75</v>
       </c>
-      <c r="O11" s="24">
+      <c r="P11" s="24">
         <f t="shared" si="2"/>
         <v>81.5</v>
       </c>
     </row>
-    <row r="12" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="12" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A12" s="19">
         <v>11</v>
       </c>
-      <c r="B12" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>37</v>
+      <c r="B12" s="20">
+        <v>1</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E12" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="19">
         <v>81</v>
       </c>
-      <c r="G12" s="19">
+      <c r="H12" s="19">
         <v>83</v>
       </c>
-      <c r="H12" s="19">
+      <c r="I12" s="19">
         <v>97</v>
       </c>
-      <c r="I12" s="19">
+      <c r="J12" s="19">
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
-      <c r="J12" s="19">
+      <c r="K12" s="19">
         <v>80</v>
       </c>
-      <c r="K12" s="19">
+      <c r="L12" s="19">
         <v>87</v>
       </c>
-      <c r="L12" s="19">
+      <c r="M12" s="19">
         <v>85</v>
       </c>
-      <c r="M12" s="19">
+      <c r="N12" s="19">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
-      <c r="N12" s="23">
+      <c r="O12" s="23">
         <v>82</v>
       </c>
-      <c r="O12" s="24">
+      <c r="P12" s="24">
         <f t="shared" si="2"/>
         <v>83.75</v>
       </c>
     </row>
-    <row r="13" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="13" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A13" s="19">
         <v>12</v>
       </c>
-      <c r="B13" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>39</v>
+      <c r="B13" s="20">
+        <v>1</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E13" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="19">
         <v>80</v>
       </c>
-      <c r="G13" s="19">
+      <c r="H13" s="19">
         <v>89</v>
       </c>
-      <c r="H13" s="19">
-        <v>90</v>
-      </c>
       <c r="I13" s="19">
+        <v>90</v>
+      </c>
+      <c r="J13" s="19">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
-      <c r="J13" s="19">
-        <v>90</v>
-      </c>
       <c r="K13" s="19">
+        <v>90</v>
+      </c>
+      <c r="L13" s="19">
         <v>86</v>
       </c>
-      <c r="L13" s="19">
+      <c r="M13" s="19">
         <v>88</v>
       </c>
-      <c r="M13" s="19">
+      <c r="N13" s="19">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="N13" s="23">
+      <c r="O13" s="23">
         <v>78</v>
       </c>
-      <c r="O13" s="24">
+      <c r="P13" s="24">
         <f t="shared" si="2"/>
         <v>82.5</v>
       </c>
     </row>
-    <row r="14" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="14" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A14" s="19">
         <v>13</v>
       </c>
-      <c r="B14" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>41</v>
+      <c r="B14" s="20">
+        <v>1</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E14" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="19">
         <v>89</v>
       </c>
-      <c r="G14" s="19">
+      <c r="H14" s="19">
         <v>93</v>
       </c>
-      <c r="H14" s="19">
+      <c r="I14" s="19">
         <v>92</v>
       </c>
-      <c r="I14" s="19">
+      <c r="J14" s="19">
         <f t="shared" si="0"/>
         <v>91</v>
-      </c>
-      <c r="J14" s="19">
-        <v>94</v>
       </c>
       <c r="K14" s="19">
         <v>94</v>
       </c>
       <c r="L14" s="19">
+        <v>94</v>
+      </c>
+      <c r="M14" s="19">
         <v>91</v>
       </c>
-      <c r="M14" s="19">
+      <c r="N14" s="19">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
-      <c r="N14" s="23">
+      <c r="O14" s="23">
         <v>85</v>
       </c>
-      <c r="O14" s="24">
+      <c r="P14" s="24">
         <f t="shared" si="2"/>
         <v>88.5</v>
       </c>
     </row>
-    <row r="15" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="15" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>43</v>
+      <c r="B15" s="20">
+        <v>1</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E15" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="19">
         <v>96</v>
       </c>
-      <c r="G15" s="19">
+      <c r="H15" s="19">
         <v>89</v>
       </c>
-      <c r="H15" s="19">
+      <c r="I15" s="19">
         <v>94</v>
       </c>
-      <c r="I15" s="19">
+      <c r="J15" s="19">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="J15" s="19">
-        <v>90</v>
-      </c>
       <c r="K15" s="19">
+        <v>90</v>
+      </c>
+      <c r="L15" s="19">
         <v>87</v>
       </c>
-      <c r="L15" s="19">
+      <c r="M15" s="19">
         <v>84</v>
       </c>
-      <c r="M15" s="19">
+      <c r="N15" s="19">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="N15" s="23">
+      <c r="O15" s="23">
         <v>86</v>
       </c>
-      <c r="O15" s="24">
+      <c r="P15" s="24">
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
     </row>
-    <row r="16" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="16" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A16" s="19">
         <v>15</v>
       </c>
-      <c r="B16" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>45</v>
+      <c r="B16" s="20">
+        <v>1</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E16" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="19">
         <v>85</v>
       </c>
-      <c r="G16" s="19">
+      <c r="H16" s="19">
         <v>96</v>
       </c>
-      <c r="H16" s="19">
+      <c r="I16" s="19">
         <v>100</v>
       </c>
-      <c r="I16" s="19">
+      <c r="J16" s="19">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="J16" s="19">
+      <c r="K16" s="19">
         <v>93</v>
       </c>
-      <c r="K16" s="19">
+      <c r="L16" s="19">
         <v>91</v>
       </c>
-      <c r="L16" s="19">
+      <c r="M16" s="19">
         <v>79</v>
       </c>
-      <c r="M16" s="19">
+      <c r="N16" s="19">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="N16" s="23">
+      <c r="O16" s="23">
         <v>81</v>
       </c>
-      <c r="O16" s="24">
+      <c r="P16" s="24">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
     </row>
-    <row r="17" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="17" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A17" s="19">
         <v>16</v>
       </c>
-      <c r="B17" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>47</v>
+      <c r="B17" s="20">
+        <v>1</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E17" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="19">
         <v>85</v>
       </c>
-      <c r="G17" s="19">
-        <v>90</v>
-      </c>
       <c r="H17" s="19">
+        <v>90</v>
+      </c>
+      <c r="I17" s="19">
         <v>95</v>
       </c>
-      <c r="I17" s="19">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
       <c r="J17" s="19">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="K17" s="19">
         <v>85</v>
       </c>
-      <c r="K17" s="19">
+      <c r="L17" s="19">
         <v>91</v>
       </c>
-      <c r="L17" s="19">
+      <c r="M17" s="19">
         <v>87</v>
       </c>
-      <c r="M17" s="19">
+      <c r="N17" s="19">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="N17" s="23">
+      <c r="O17" s="23">
         <v>75</v>
       </c>
-      <c r="O17" s="24">
+      <c r="P17" s="24">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
     </row>
-    <row r="18" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="18" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A18" s="19">
         <v>17</v>
       </c>
-      <c r="B18" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>49</v>
+      <c r="B18" s="20">
+        <v>1</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E18" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="19">
         <v>96</v>
       </c>
-      <c r="G18" s="19">
+      <c r="H18" s="19">
         <v>87</v>
       </c>
-      <c r="H18" s="19">
+      <c r="I18" s="19">
         <v>93</v>
       </c>
-      <c r="I18" s="19">
+      <c r="J18" s="19">
         <f t="shared" si="0"/>
         <v>92</v>
       </c>
-      <c r="J18" s="19">
+      <c r="K18" s="19">
         <v>94</v>
       </c>
-      <c r="K18" s="19">
+      <c r="L18" s="19">
         <v>81</v>
       </c>
-      <c r="L18" s="19">
+      <c r="M18" s="19">
         <v>89</v>
       </c>
-      <c r="M18" s="19">
+      <c r="N18" s="19">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="N18" s="23">
+      <c r="O18" s="23">
         <v>92</v>
       </c>
-      <c r="O18" s="24">
+      <c r="P18" s="24">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
     </row>
-    <row r="19" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="19" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A19" s="19">
         <v>18</v>
       </c>
-      <c r="B19" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>51</v>
+      <c r="B19" s="20">
+        <v>1</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E19" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="19">
         <v>56</v>
       </c>
-      <c r="G19" s="19">
+      <c r="H19" s="19">
         <v>92</v>
       </c>
-      <c r="H19" s="19">
+      <c r="I19" s="19">
         <v>88</v>
       </c>
-      <c r="I19" s="19">
+      <c r="J19" s="19">
         <f t="shared" si="0"/>
         <v>79</v>
       </c>
-      <c r="J19" s="19">
-        <v>90</v>
-      </c>
       <c r="K19" s="19">
+        <v>90</v>
+      </c>
+      <c r="L19" s="19">
         <v>84</v>
       </c>
-      <c r="L19" s="19">
+      <c r="M19" s="19">
         <v>85</v>
       </c>
-      <c r="M19" s="19">
+      <c r="N19" s="19">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
-      <c r="N19" s="23">
+      <c r="O19" s="23">
         <v>89</v>
       </c>
-      <c r="O19" s="24">
+      <c r="P19" s="24">
         <f t="shared" si="2"/>
         <v>85.75</v>
       </c>
     </row>
-    <row r="20" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="20" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A20" s="19">
         <v>19</v>
       </c>
-      <c r="B20" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>53</v>
+      <c r="B20" s="20">
+        <v>1</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E20" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20" s="19">
         <v>91</v>
-      </c>
-      <c r="G20" s="19">
-        <v>89</v>
       </c>
       <c r="H20" s="19">
         <v>89</v>
       </c>
       <c r="I20" s="19">
-        <f t="shared" si="0"/>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J20" s="19">
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
       <c r="K20" s="19">
+        <v>90</v>
+      </c>
+      <c r="L20" s="19">
         <v>85</v>
       </c>
-      <c r="L20" s="19">
+      <c r="M20" s="19">
         <v>86</v>
       </c>
-      <c r="M20" s="19">
+      <c r="N20" s="19">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="N20" s="23">
+      <c r="O20" s="23">
         <v>92</v>
       </c>
-      <c r="O20" s="24">
+      <c r="P20" s="24">
         <f t="shared" si="2"/>
         <v>90.25</v>
       </c>
     </row>
-    <row r="21" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="21" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A21" s="19">
         <v>20</v>
       </c>
-      <c r="B21" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>55</v>
+      <c r="B21" s="20">
+        <v>1</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E21" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" s="19">
         <v>84</v>
       </c>
-      <c r="G21" s="19">
+      <c r="H21" s="19">
         <v>94</v>
       </c>
-      <c r="H21" s="19">
+      <c r="I21" s="19">
         <v>92</v>
       </c>
-      <c r="I21" s="19">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
       <c r="J21" s="19">
-        <v>85</v>
+        <f t="shared" si="0"/>
+        <v>90</v>
       </c>
       <c r="K21" s="19">
         <v>85</v>
       </c>
       <c r="L21" s="19">
+        <v>85</v>
+      </c>
+      <c r="M21" s="19">
         <v>80</v>
       </c>
-      <c r="M21" s="19">
+      <c r="N21" s="19">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
-      <c r="N21" s="23">
+      <c r="O21" s="23">
         <v>80</v>
       </c>
-      <c r="O21" s="24">
+      <c r="P21" s="24">
         <f t="shared" si="2"/>
         <v>83.25</v>
       </c>
     </row>
-    <row r="22" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="22" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A22" s="19">
         <v>21</v>
       </c>
-      <c r="B22" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>57</v>
+      <c r="B22" s="20">
+        <v>1</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E22" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" s="19">
         <v>77</v>
       </c>
-      <c r="G22" s="19">
+      <c r="H22" s="19">
         <v>95</v>
       </c>
-      <c r="H22" s="19">
+      <c r="I22" s="19">
         <v>92</v>
       </c>
-      <c r="I22" s="19">
+      <c r="J22" s="19">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="J22" s="19">
+      <c r="K22" s="19">
         <v>80</v>
       </c>
-      <c r="K22" s="19">
+      <c r="L22" s="19">
         <v>84</v>
       </c>
-      <c r="L22" s="19">
+      <c r="M22" s="19">
         <v>87</v>
       </c>
-      <c r="M22" s="19">
+      <c r="N22" s="19">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
-      <c r="N22" s="23">
+      <c r="O22" s="23">
         <v>65</v>
       </c>
-      <c r="O22" s="24">
+      <c r="P22" s="24">
         <f t="shared" si="2"/>
         <v>75.5</v>
       </c>
     </row>
-    <row r="23" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="23" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A23" s="19">
         <v>22</v>
       </c>
-      <c r="B23" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="22" t="s">
+      <c r="B23" s="20">
+        <v>1</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23" s="19">
         <v>96</v>
       </c>
-      <c r="G23" s="19">
+      <c r="H23" s="19">
         <v>95</v>
       </c>
-      <c r="H23" s="19">
+      <c r="I23" s="19">
         <v>97</v>
       </c>
-      <c r="I23" s="19">
+      <c r="J23" s="19">
         <f t="shared" si="0"/>
         <v>96</v>
-      </c>
-      <c r="J23" s="19">
-        <v>95</v>
       </c>
       <c r="K23" s="19">
         <v>95</v>
       </c>
       <c r="L23" s="19">
+        <v>95</v>
+      </c>
+      <c r="M23" s="19">
         <v>93</v>
       </c>
-      <c r="M23" s="19">
+      <c r="N23" s="19">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
-      <c r="N23" s="23">
+      <c r="O23" s="23">
         <v>80</v>
       </c>
-      <c r="O23" s="24">
+      <c r="P23" s="24">
         <f t="shared" si="2"/>
         <v>87.5</v>
       </c>
     </row>
-    <row r="24" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="24" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A24" s="19">
         <v>23</v>
       </c>
-      <c r="B24" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>61</v>
+      <c r="B24" s="20">
+        <v>1</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E24" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24" s="19">
         <v>95</v>
       </c>
-      <c r="G24" s="19">
+      <c r="H24" s="19">
         <v>92</v>
       </c>
-      <c r="H24" s="19">
+      <c r="I24" s="19">
         <v>97</v>
       </c>
-      <c r="I24" s="19">
+      <c r="J24" s="19">
         <f t="shared" si="0"/>
         <v>95</v>
-      </c>
-      <c r="J24" s="19">
-        <v>94</v>
       </c>
       <c r="K24" s="19">
         <v>94</v>
       </c>
       <c r="L24" s="19">
+        <v>94</v>
+      </c>
+      <c r="M24" s="19">
         <v>91</v>
       </c>
-      <c r="M24" s="19">
+      <c r="N24" s="19">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
-      <c r="N24" s="23">
+      <c r="O24" s="23">
         <v>79.5194805194805</v>
       </c>
-      <c r="O24" s="24">
+      <c r="P24" s="24">
         <f t="shared" si="2"/>
         <v>86.7597402597403</v>
       </c>
     </row>
-    <row r="25" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="25" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A25" s="19">
         <v>24</v>
       </c>
-      <c r="B25" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>63</v>
+      <c r="B25" s="20">
+        <v>1</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>17</v>
       </c>
       <c r="E25" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="G25" s="19">
         <v>42</v>
       </c>
-      <c r="G25" s="19">
+      <c r="H25" s="19">
         <v>84</v>
       </c>
-      <c r="H25" s="19">
+      <c r="I25" s="19">
         <v>86</v>
       </c>
-      <c r="I25" s="19">
+      <c r="J25" s="19">
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="J25" s="19">
+      <c r="K25" s="19">
         <v>94</v>
       </c>
-      <c r="K25" s="19">
+      <c r="L25" s="19">
         <v>84</v>
       </c>
-      <c r="L25" s="19">
-        <v>90</v>
-      </c>
       <c r="M25" s="19">
+        <v>90</v>
+      </c>
+      <c r="N25" s="19">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="N25" s="23">
+      <c r="O25" s="23">
         <v>79.3709768492377</v>
       </c>
-      <c r="O25" s="24">
+      <c r="P25" s="24">
         <f t="shared" si="2"/>
         <v>79.6854884246189</v>
       </c>
     </row>
-    <row r="26" s="16" customFormat="1" ht="22" customHeight="1" spans="1:15">
+    <row r="26" s="16" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A26" s="19">
         <v>25</v>
       </c>
-      <c r="B26" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="22" t="s">
+      <c r="B26" s="20">
+        <v>1</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="G26" s="19">
         <v>43</v>
       </c>
-      <c r="G26" s="19">
+      <c r="H26" s="19">
         <v>95</v>
       </c>
-      <c r="H26" s="19">
+      <c r="I26" s="19">
         <v>94</v>
       </c>
-      <c r="I26" s="19">
+      <c r="J26" s="19">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="J26" s="19">
+      <c r="K26" s="19">
         <v>80</v>
       </c>
-      <c r="K26" s="19">
+      <c r="L26" s="19">
         <v>86</v>
       </c>
-      <c r="L26" s="19">
+      <c r="M26" s="19">
         <v>85</v>
       </c>
-      <c r="M26" s="19">
+      <c r="N26" s="19">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
-      <c r="N26" s="23">
+      <c r="O26" s="23">
         <v>79.2224731789949</v>
       </c>
-      <c r="O26" s="24">
+      <c r="P26" s="24">
         <f t="shared" si="2"/>
         <v>79.8612365894975</v>
       </c>
@@ -2922,19 +3003,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="13.6272727272727" customWidth="1"/>
-    <col min="3" max="4" width="14.6272727272727" customWidth="1"/>
-    <col min="5" max="5" width="13.7545454545455" customWidth="1"/>
-    <col min="6" max="6" width="12.7545454545455" customWidth="1"/>
-    <col min="8" max="8" width="9.62727272727273"/>
-    <col min="10" max="10" width="11.2545454545455" customWidth="1"/>
-    <col min="11" max="11" width="13.8727272727273" customWidth="1"/>
+    <col min="2" max="3" width="13.6272727272727" customWidth="1"/>
+    <col min="4" max="5" width="14.6272727272727" customWidth="1"/>
+    <col min="6" max="6" width="13.7545454545455" customWidth="1"/>
+    <col min="7" max="7" width="12.7545454545455" customWidth="1"/>
+    <col min="9" max="9" width="9.62727272727273"/>
+    <col min="11" max="11" width="11.2545454545455" customWidth="1"/>
+    <col min="12" max="12" width="13.8727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19" spans="1:15">
+    <row r="1" ht="19" spans="1:16">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2950,16 +3031,16 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
@@ -2974,1002 +3055,1067 @@
       <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" customFormat="1" spans="1:15">
+      <c r="P1" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" spans="1:16">
       <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="9" t="s">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="9">
         <v>71</v>
       </c>
-      <c r="G2" s="9">
+      <c r="H2" s="9">
         <v>94</v>
       </c>
-      <c r="H2" s="9">
+      <c r="I2" s="9">
         <v>93</v>
       </c>
-      <c r="I2" s="9">
-        <f>ROUND(AVERAGE(F2:H2),0)</f>
+      <c r="J2" s="9">
+        <f>ROUND(AVERAGE(G2:I2),0)</f>
         <v>86</v>
       </c>
-      <c r="J2" s="9">
+      <c r="K2" s="9">
         <v>82</v>
       </c>
-      <c r="K2" s="9">
+      <c r="L2" s="9">
         <v>86</v>
       </c>
-      <c r="L2" s="9">
+      <c r="M2" s="9">
         <v>87</v>
       </c>
-      <c r="M2" s="9">
-        <f>ROUND(AVERAGE(J2:L2),0)</f>
+      <c r="N2" s="9">
+        <f>ROUND(AVERAGE(K2:M2),0)</f>
         <v>85</v>
       </c>
-      <c r="N2">
-        <f>G2-3</f>
+      <c r="O2">
+        <f>H2-3</f>
         <v>91</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
+    <row r="3" customFormat="1" ht="16.35" customHeight="1" spans="1:16">
       <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="9">
         <v>94</v>
       </c>
-      <c r="G3" s="9">
+      <c r="H3" s="9">
         <v>88</v>
       </c>
-      <c r="H3" s="9">
+      <c r="I3" s="9">
         <v>87</v>
       </c>
-      <c r="I3" s="9">
-        <f t="shared" ref="I3:I22" si="0">ROUND(AVERAGE(F3:H3),0)</f>
-        <v>90</v>
-      </c>
       <c r="J3" s="9">
+        <f t="shared" ref="J3:J22" si="0">ROUND(AVERAGE(G3:I3),0)</f>
         <v>90</v>
       </c>
       <c r="K3" s="9">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L3" s="9">
         <v>88</v>
       </c>
       <c r="M3" s="9">
-        <f t="shared" ref="M3:M22" si="1">ROUND(AVERAGE(J3:L3),0)</f>
+        <v>88</v>
+      </c>
+      <c r="N3" s="9">
+        <f t="shared" ref="N3:N22" si="1">ROUND(AVERAGE(K3:M3),0)</f>
         <v>89</v>
       </c>
-      <c r="N3">
-        <f t="shared" ref="N3:N22" si="2">G3-3</f>
+      <c r="O3">
+        <f t="shared" ref="O3:O22" si="2">H3-3</f>
         <v>85</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
+    <row r="4" customFormat="1" ht="16.35" customHeight="1" spans="1:16">
       <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="9">
         <v>87</v>
       </c>
-      <c r="G4" s="9">
+      <c r="H4" s="9">
         <v>86</v>
       </c>
-      <c r="H4" s="9">
+      <c r="I4" s="9">
         <v>87</v>
       </c>
-      <c r="I4" s="9">
+      <c r="J4" s="9">
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
-      <c r="J4" s="9">
-        <v>90</v>
-      </c>
       <c r="K4" s="9">
         <v>90</v>
       </c>
       <c r="L4" s="9">
+        <v>90</v>
+      </c>
+      <c r="M4" s="9">
         <v>91</v>
       </c>
-      <c r="M4" s="9">
-        <f t="shared" si="1"/>
-        <v>90</v>
-      </c>
-      <c r="N4">
+      <c r="N4" s="9">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="O4">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
     </row>
-    <row r="5" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
+    <row r="5" customFormat="1" ht="16.35" customHeight="1" spans="1:16">
       <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="9">
-        <v>90</v>
+      <c r="F5" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="G5" s="9">
+        <v>90</v>
+      </c>
+      <c r="H5" s="9">
         <v>93</v>
       </c>
-      <c r="H5" s="9">
+      <c r="I5" s="9">
         <v>91</v>
       </c>
-      <c r="I5" s="9">
+      <c r="J5" s="9">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="J5" s="9">
+      <c r="K5" s="9">
         <v>91</v>
       </c>
-      <c r="K5" s="9">
-        <v>90</v>
-      </c>
       <c r="L5" s="9">
         <v>90</v>
       </c>
       <c r="M5" s="9">
-        <f t="shared" si="1"/>
-        <v>90</v>
-      </c>
-      <c r="N5">
-        <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
+        <v>90</v>
+      </c>
+      <c r="N5" s="9">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="16.35" customHeight="1" spans="1:16">
       <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="9">
-        <v>90</v>
+      <c r="F6" s="9" t="s">
+        <v>77</v>
       </c>
       <c r="G6" s="9">
+        <v>90</v>
+      </c>
+      <c r="H6" s="9">
         <v>92</v>
       </c>
-      <c r="H6" s="9">
+      <c r="I6" s="9">
         <v>96</v>
       </c>
-      <c r="I6" s="9">
+      <c r="J6" s="9">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="J6" s="9">
+      <c r="K6" s="9">
         <v>88</v>
       </c>
-      <c r="K6" s="9">
-        <v>90</v>
-      </c>
       <c r="L6" s="9">
         <v>90</v>
       </c>
       <c r="M6" s="9">
+        <v>90</v>
+      </c>
+      <c r="N6" s="9">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
+    <row r="7" customFormat="1" ht="16.35" customHeight="1" spans="1:16">
       <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="9">
         <v>92</v>
       </c>
-      <c r="G7" s="9">
+      <c r="H7" s="9">
         <v>93</v>
       </c>
-      <c r="H7" s="9">
+      <c r="I7" s="9">
         <v>91</v>
       </c>
-      <c r="I7" s="9">
+      <c r="J7" s="9">
         <f t="shared" si="0"/>
         <v>92</v>
       </c>
-      <c r="J7" s="9">
+      <c r="K7" s="9">
         <v>84</v>
       </c>
-      <c r="K7" s="9">
-        <v>90</v>
-      </c>
       <c r="L7" s="9">
+        <v>90</v>
+      </c>
+      <c r="M7" s="9">
         <v>91</v>
       </c>
-      <c r="M7" s="9">
+      <c r="N7" s="9">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="N7">
-        <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
+      <c r="O7">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" ht="16.35" customHeight="1" spans="1:16">
       <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" s="9" t="s">
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" s="9">
         <v>86</v>
       </c>
-      <c r="G8" s="9">
+      <c r="H8" s="9">
         <v>93</v>
       </c>
-      <c r="H8" s="9">
+      <c r="I8" s="9">
         <v>85</v>
       </c>
-      <c r="I8" s="9">
+      <c r="J8" s="9">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="J8" s="9">
+      <c r="K8" s="9">
         <v>88</v>
       </c>
-      <c r="K8" s="9">
+      <c r="L8" s="9">
         <v>87</v>
       </c>
-      <c r="L8" s="9">
+      <c r="M8" s="9">
         <v>88</v>
       </c>
-      <c r="M8" s="9">
+      <c r="N8" s="9">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="N8">
-        <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
+      <c r="O8">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" ht="16.35" customHeight="1" spans="1:16">
       <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" s="9" t="s">
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="9">
         <v>96</v>
       </c>
-      <c r="G9" s="9">
+      <c r="H9" s="9">
         <v>93</v>
       </c>
-      <c r="H9" s="9">
+      <c r="I9" s="9">
         <v>96</v>
       </c>
-      <c r="I9" s="9">
+      <c r="J9" s="9">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="J9" s="9">
-        <v>90</v>
-      </c>
       <c r="K9" s="9">
+        <v>90</v>
+      </c>
+      <c r="L9" s="9">
         <v>89</v>
       </c>
-      <c r="L9" s="9">
+      <c r="M9" s="9">
         <v>92</v>
       </c>
-      <c r="M9" s="9">
-        <f t="shared" si="1"/>
-        <v>90</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
+      <c r="N9" s="9">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" ht="16.35" customHeight="1" spans="1:16">
       <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="9">
         <v>95</v>
       </c>
-      <c r="G10" s="9">
+      <c r="H10" s="9">
         <v>93</v>
       </c>
-      <c r="H10" s="9">
+      <c r="I10" s="9">
         <v>95</v>
       </c>
-      <c r="I10" s="9">
+      <c r="J10" s="9">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="J10" s="9">
+      <c r="K10" s="9">
         <v>91</v>
-      </c>
-      <c r="K10" s="9">
-        <v>94</v>
       </c>
       <c r="L10" s="9">
         <v>94</v>
       </c>
       <c r="M10" s="9">
+        <v>94</v>
+      </c>
+      <c r="N10" s="9">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
-      <c r="N10">
-        <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
+      <c r="O10">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" ht="16.35" customHeight="1" spans="1:16">
       <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="9">
+        <v>69</v>
+      </c>
+      <c r="H11" s="9">
+        <v>92</v>
+      </c>
+      <c r="I11" s="9">
+        <v>82</v>
+      </c>
+      <c r="J11" s="9">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="K11" s="9">
         <v>85</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F11" s="9">
-        <v>69</v>
-      </c>
-      <c r="G11" s="9">
-        <v>92</v>
-      </c>
-      <c r="H11" s="9">
-        <v>82</v>
-      </c>
-      <c r="I11" s="9">
-        <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-      <c r="J11" s="9">
-        <v>85</v>
-      </c>
-      <c r="K11" s="9">
-        <v>90</v>
-      </c>
       <c r="L11" s="9">
+        <v>90</v>
+      </c>
+      <c r="M11" s="9">
         <v>91</v>
       </c>
-      <c r="M11" s="9">
+      <c r="N11" s="9">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
     </row>
-    <row r="12" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
+    <row r="12" customFormat="1" ht="16.35" customHeight="1" spans="1:16">
       <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" s="9" t="s">
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="9">
         <v>95</v>
       </c>
-      <c r="G12" s="9">
+      <c r="H12" s="9">
         <v>94</v>
       </c>
-      <c r="H12" s="9">
+      <c r="I12" s="9">
         <v>96</v>
       </c>
-      <c r="I12" s="9">
+      <c r="J12" s="9">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="J12" s="9">
+      <c r="K12" s="9">
         <v>94</v>
-      </c>
-      <c r="K12" s="9">
-        <v>92</v>
       </c>
       <c r="L12" s="9">
         <v>92</v>
       </c>
       <c r="M12" s="9">
+        <v>92</v>
+      </c>
+      <c r="N12" s="9">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
     </row>
-    <row r="13" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
+    <row r="13" customFormat="1" ht="16.35" customHeight="1" spans="1:16">
       <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="7" t="s">
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13" s="9">
+        <v>92</v>
+      </c>
+      <c r="H13" s="9">
+        <v>87</v>
+      </c>
+      <c r="I13" s="9">
+        <v>90</v>
+      </c>
+      <c r="J13" s="9">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="K13" s="9">
         <v>89</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="F13" s="9">
+      <c r="L13" s="9">
+        <v>90</v>
+      </c>
+      <c r="M13" s="9">
         <v>92</v>
       </c>
-      <c r="G13" s="9">
-        <v>87</v>
-      </c>
-      <c r="H13" s="9">
-        <v>90</v>
-      </c>
-      <c r="I13" s="9">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-      <c r="J13" s="9">
-        <v>89</v>
-      </c>
-      <c r="K13" s="9">
-        <v>90</v>
-      </c>
-      <c r="L13" s="9">
-        <v>92</v>
-      </c>
-      <c r="M13" s="9">
-        <f t="shared" si="1"/>
-        <v>90</v>
-      </c>
-      <c r="N13">
+      <c r="N13" s="9">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="O13">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
     </row>
-    <row r="14" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
+    <row r="14" customFormat="1" ht="16.35" customHeight="1" spans="1:16">
       <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" s="9" t="s">
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="9">
         <v>95</v>
       </c>
-      <c r="G14" s="9">
+      <c r="H14" s="9">
         <v>84</v>
       </c>
-      <c r="H14" s="9">
+      <c r="I14" s="9">
         <v>92</v>
       </c>
-      <c r="I14" s="9">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
       <c r="J14" s="9">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="K14" s="9">
         <v>86</v>
       </c>
-      <c r="K14" s="9">
+      <c r="L14" s="9">
         <v>89</v>
       </c>
-      <c r="L14" s="9">
-        <v>90</v>
-      </c>
       <c r="M14" s="9">
+        <v>90</v>
+      </c>
+      <c r="N14" s="9">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
     </row>
-    <row r="15" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
+    <row r="15" customFormat="1" ht="16.35" customHeight="1" spans="1:16">
       <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E15" s="9" t="s">
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="9">
         <v>73</v>
       </c>
-      <c r="G15" s="9">
-        <v>90</v>
-      </c>
       <c r="H15" s="9">
+        <v>90</v>
+      </c>
+      <c r="I15" s="9">
         <v>92</v>
       </c>
-      <c r="I15" s="9">
+      <c r="J15" s="9">
         <f t="shared" si="0"/>
         <v>85</v>
-      </c>
-      <c r="J15" s="9">
-        <v>87</v>
       </c>
       <c r="K15" s="9">
         <v>87</v>
       </c>
       <c r="L15" s="9">
+        <v>87</v>
+      </c>
+      <c r="M15" s="9">
         <v>88</v>
       </c>
-      <c r="M15" s="9">
+      <c r="N15" s="9">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
     </row>
-    <row r="16" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
+    <row r="16" customFormat="1" ht="16.35" customHeight="1" spans="1:16">
       <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="7" t="s">
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" s="9">
         <v>95</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F16" s="9">
+      <c r="H16" s="9">
+        <v>93</v>
+      </c>
+      <c r="I16" s="9">
+        <v>98</v>
+      </c>
+      <c r="J16" s="9">
+        <f t="shared" si="0"/>
         <v>95</v>
-      </c>
-      <c r="G16" s="9">
-        <v>93</v>
-      </c>
-      <c r="H16" s="9">
-        <v>98</v>
-      </c>
-      <c r="I16" s="9">
-        <f t="shared" si="0"/>
-        <v>95</v>
-      </c>
-      <c r="J16" s="9">
-        <v>94</v>
       </c>
       <c r="K16" s="9">
         <v>94</v>
       </c>
       <c r="L16" s="9">
+        <v>94</v>
+      </c>
+      <c r="M16" s="9">
         <v>91</v>
       </c>
-      <c r="M16" s="9">
+      <c r="N16" s="9">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
-      <c r="N16">
-        <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" ht="16.35" customHeight="1" spans="1:14">
+      <c r="O16">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
       <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="7" t="s">
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="9">
+        <v>86</v>
+      </c>
+      <c r="H17" s="9">
+        <v>89</v>
+      </c>
+      <c r="I17" s="9">
         <v>97</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" s="9">
+      <c r="J17" s="9">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="K17" s="9">
+        <v>95</v>
+      </c>
+      <c r="L17" s="9">
+        <v>90</v>
+      </c>
+      <c r="M17" s="9">
+        <v>91</v>
+      </c>
+      <c r="N17" s="9">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="2"/>
         <v>86</v>
       </c>
-      <c r="G17" s="9">
+    </row>
+    <row r="18" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
+      <c r="A18" s="7">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G18" s="9">
+        <v>97</v>
+      </c>
+      <c r="H18" s="9">
+        <v>91</v>
+      </c>
+      <c r="I18" s="9">
+        <v>96</v>
+      </c>
+      <c r="J18" s="9">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+      <c r="K18" s="9">
         <v>89</v>
       </c>
-      <c r="H17" s="9">
-        <v>97</v>
-      </c>
-      <c r="I17" s="9">
-        <f t="shared" si="0"/>
-        <v>91</v>
-      </c>
-      <c r="J17" s="9">
-        <v>95</v>
-      </c>
-      <c r="K17" s="9">
-        <v>90</v>
-      </c>
-      <c r="L17" s="9">
-        <v>91</v>
-      </c>
-      <c r="M17" s="9">
-        <f t="shared" si="1"/>
+      <c r="L18" s="9">
         <v>92</v>
       </c>
-      <c r="N17">
-        <f t="shared" si="2"/>
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" ht="16.35" customHeight="1" spans="1:14">
-      <c r="A18" s="7">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F18" s="9">
-        <v>97</v>
-      </c>
-      <c r="G18" s="9">
-        <v>91</v>
-      </c>
-      <c r="H18" s="9">
-        <v>96</v>
-      </c>
-      <c r="I18" s="9">
-        <f t="shared" si="0"/>
-        <v>95</v>
-      </c>
-      <c r="J18" s="9">
-        <v>89</v>
-      </c>
-      <c r="K18" s="9">
-        <v>92</v>
-      </c>
-      <c r="L18" s="9">
-        <v>90</v>
-      </c>
       <c r="M18" s="9">
-        <f t="shared" si="1"/>
-        <v>90</v>
-      </c>
-      <c r="N18">
+        <v>90</v>
+      </c>
+      <c r="N18" s="9">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="O18">
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
     </row>
-    <row r="19" customFormat="1" ht="16.35" customHeight="1" spans="1:14">
+    <row r="19" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
       <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E19" s="9" t="s">
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G19" s="9">
         <v>92</v>
       </c>
-      <c r="G19" s="9">
+      <c r="H19" s="9">
         <v>95</v>
       </c>
-      <c r="H19" s="9">
+      <c r="I19" s="9">
         <v>92</v>
       </c>
-      <c r="I19" s="9">
+      <c r="J19" s="9">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="J19" s="9">
-        <v>90</v>
-      </c>
       <c r="K19" s="9">
         <v>90</v>
       </c>
       <c r="L19" s="9">
+        <v>90</v>
+      </c>
+      <c r="M19" s="9">
         <v>89</v>
       </c>
-      <c r="M19" s="9">
-        <f t="shared" si="1"/>
-        <v>90</v>
-      </c>
-      <c r="N19">
+      <c r="N19" s="9">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="O19">
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
     </row>
-    <row r="20" customFormat="1" ht="16.35" customHeight="1" spans="1:14">
+    <row r="20" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
       <c r="A20" s="7">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E20" s="9" t="s">
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="G20" s="9">
         <v>88</v>
       </c>
-      <c r="G20" s="9">
+      <c r="H20" s="9">
         <v>93</v>
       </c>
-      <c r="H20" s="9">
+      <c r="I20" s="9">
         <v>97</v>
       </c>
-      <c r="I20" s="9">
+      <c r="J20" s="9">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="J20" s="9">
+      <c r="K20" s="9">
         <v>89</v>
       </c>
-      <c r="K20" s="9">
+      <c r="L20" s="9">
         <v>82</v>
       </c>
-      <c r="L20" s="9">
+      <c r="M20" s="9">
         <v>85</v>
       </c>
-      <c r="M20" s="9">
+      <c r="N20" s="9">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
-      <c r="N20">
-        <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" ht="16.35" customHeight="1" spans="1:14">
+      <c r="O20">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
       <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E21" s="9" t="s">
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G21" s="9">
         <v>94</v>
       </c>
-      <c r="G21" s="9">
+      <c r="H21" s="9">
         <v>97</v>
       </c>
-      <c r="H21" s="9">
+      <c r="I21" s="9">
         <v>91</v>
       </c>
-      <c r="I21" s="9">
+      <c r="J21" s="9">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="J21" s="9">
-        <v>90</v>
-      </c>
       <c r="K21" s="9">
+        <v>90</v>
+      </c>
+      <c r="L21" s="9">
         <v>93</v>
       </c>
-      <c r="L21" s="9">
+      <c r="M21" s="9">
         <v>92</v>
       </c>
-      <c r="M21" s="9">
+      <c r="N21" s="9">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <f t="shared" si="2"/>
         <v>94</v>
       </c>
     </row>
-    <row r="22" customFormat="1" ht="16.35" customHeight="1" spans="1:14">
+    <row r="22" customFormat="1" ht="16.35" customHeight="1" spans="1:15">
       <c r="A22" s="7">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" s="9" t="s">
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="G22" s="9">
         <v>41</v>
       </c>
-      <c r="G22" s="9">
+      <c r="H22" s="9">
         <v>87</v>
       </c>
-      <c r="H22" s="9">
+      <c r="I22" s="9">
         <v>71</v>
       </c>
-      <c r="I22" s="9">
+      <c r="J22" s="9">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="J22" s="9">
+      <c r="K22" s="9">
         <v>81</v>
       </c>
-      <c r="K22" s="9">
+      <c r="L22" s="9">
         <v>80</v>
       </c>
-      <c r="L22" s="9">
+      <c r="M22" s="9">
         <v>81</v>
       </c>
-      <c r="M22" s="9">
+      <c r="N22" s="9">
         <f t="shared" si="1"/>
         <v>81</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
     </row>
-    <row r="23" customFormat="1" ht="25" customHeight="1" spans="1:14">
-      <c r="E23" s="13"/>
+    <row r="23" customFormat="1" ht="25" customHeight="1" spans="1:15">
       <c r="F23" s="13"/>
       <c r="G23" s="13"/>
       <c r="H23" s="13"/>
@@ -3977,6 +4123,7 @@
       <c r="J23" s="13"/>
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3988,24 +4135,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="4.22727272727273" customWidth="1"/>
-    <col min="2" max="2" width="11.4363636363636" customWidth="1"/>
-    <col min="3" max="3" width="13.3454545454545" customWidth="1"/>
-    <col min="4" max="4" width="11.4363636363636" customWidth="1"/>
-    <col min="5" max="5" width="8.45454545454546" customWidth="1"/>
-    <col min="6" max="6" width="12.4454545454545" customWidth="1"/>
-    <col min="7" max="7" width="11.1818181818182" customWidth="1"/>
-    <col min="9" max="9" width="12.6272727272727"/>
-    <col min="10" max="10" width="7.78181818181818" customWidth="1"/>
-    <col min="11" max="11" width="11.8818181818182" customWidth="1"/>
-    <col min="12" max="12" width="7.97272727272727" customWidth="1"/>
-    <col min="15" max="15" width="9" style="2"/>
+    <col min="2" max="3" width="11.4363636363636" customWidth="1"/>
+    <col min="4" max="4" width="13.3454545454545" customWidth="1"/>
+    <col min="5" max="5" width="11.4363636363636" customWidth="1"/>
+    <col min="6" max="6" width="8.45454545454546" customWidth="1"/>
+    <col min="7" max="7" width="12.4454545454545" customWidth="1"/>
+    <col min="8" max="8" width="11.1818181818182" customWidth="1"/>
+    <col min="10" max="10" width="12.6272727272727"/>
+    <col min="11" max="11" width="7.78181818181818" customWidth="1"/>
+    <col min="12" max="12" width="11.8818181818182" customWidth="1"/>
+    <col min="13" max="13" width="7.97272727272727" customWidth="1"/>
+    <col min="16" max="16" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="9.5" spans="1:15">
+    <row r="1" s="1" customFormat="1" ht="9.5" spans="1:16">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4021,16 +4168,16 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
@@ -4045,894 +4192,948 @@
       <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" ht="16.35" customHeight="1" spans="1:15">
+      <c r="P1" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" ht="16.35" customHeight="1" spans="1:16">
       <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>109</v>
+      <c r="B2" s="7">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F2" s="7">
-        <v>96</v>
+      <c r="F2" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G2" s="7">
         <v>96</v>
       </c>
-      <c r="H2" s="9">
-        <v>90</v>
-      </c>
-      <c r="I2" s="10">
-        <f>ROUND(AVERAGE(F2:H2),0)</f>
+      <c r="H2" s="7">
+        <v>96</v>
+      </c>
+      <c r="I2" s="9">
+        <v>90</v>
+      </c>
+      <c r="J2" s="10">
+        <f>ROUND(AVERAGE(G2:I2),0)</f>
         <v>94</v>
       </c>
-      <c r="J2" s="10">
+      <c r="K2" s="10">
         <v>92</v>
       </c>
-      <c r="K2" s="10">
-        <v>90</v>
-      </c>
       <c r="L2" s="10">
         <v>90</v>
       </c>
       <c r="M2" s="10">
-        <f>ROUND(AVERAGE(J2:L2),0)</f>
+        <v>90</v>
+      </c>
+      <c r="N2" s="10">
+        <f>ROUND(AVERAGE(K2:M2),0)</f>
         <v>91</v>
       </c>
-      <c r="N2" s="11">
+      <c r="O2" s="11">
         <v>95</v>
       </c>
-      <c r="O2" s="12">
-        <f>0.25*I2+0.25*M2+0.5*N2</f>
+      <c r="P2" s="12">
+        <f>0.25*J2+0.25*N2+0.5*O2</f>
         <v>93.75</v>
       </c>
     </row>
-    <row r="3" ht="16.35" customHeight="1" spans="1:15">
+    <row r="3" ht="16.35" customHeight="1" spans="1:16">
       <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>111</v>
+      <c r="B3" s="7">
+        <v>1</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="F3" s="7">
-        <v>90</v>
+      <c r="F3" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="G3" s="7">
+        <v>90</v>
+      </c>
+      <c r="H3" s="7">
         <v>98</v>
       </c>
-      <c r="H3" s="9">
+      <c r="I3" s="9">
         <v>96</v>
       </c>
-      <c r="I3" s="10">
-        <f t="shared" ref="I3:I23" si="0">ROUND(AVERAGE(F3:H3),0)</f>
+      <c r="J3" s="10">
+        <f t="shared" ref="J3:J23" si="0">ROUND(AVERAGE(G3:I3),0)</f>
         <v>95</v>
-      </c>
-      <c r="J3" s="10">
-        <v>89</v>
       </c>
       <c r="K3" s="10">
         <v>89</v>
       </c>
       <c r="L3" s="10">
+        <v>89</v>
+      </c>
+      <c r="M3" s="10">
         <v>88</v>
       </c>
-      <c r="M3" s="10">
-        <f t="shared" ref="M3:M23" si="1">ROUND(AVERAGE(J3:L3),0)</f>
+      <c r="N3" s="10">
+        <f t="shared" ref="N3:N23" si="1">ROUND(AVERAGE(K3:M3),0)</f>
         <v>89</v>
       </c>
-      <c r="N3" s="11">
-        <v>90</v>
-      </c>
-      <c r="O3" s="12">
-        <f t="shared" ref="O3:O23" si="2">0.25*I3+0.25*M3+0.5*N3</f>
+      <c r="O3" s="11">
+        <v>90</v>
+      </c>
+      <c r="P3" s="12">
+        <f t="shared" ref="P3:P23" si="2">0.25*J3+0.25*N3+0.5*O3</f>
         <v>91</v>
       </c>
     </row>
-    <row r="4" ht="16.35" customHeight="1" spans="1:15">
+    <row r="4" ht="16.35" customHeight="1" spans="1:16">
       <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>113</v>
+      <c r="B4" s="7">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="G4" s="7">
         <v>69</v>
       </c>
-      <c r="G4" s="7">
+      <c r="H4" s="7">
         <v>94</v>
       </c>
-      <c r="H4" s="9">
-        <v>90</v>
-      </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
+        <v>90</v>
+      </c>
+      <c r="J4" s="10">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="J4" s="10">
-        <v>90</v>
-      </c>
       <c r="K4" s="10">
         <v>90</v>
       </c>
       <c r="L4" s="10">
+        <v>90</v>
+      </c>
+      <c r="M4" s="10">
         <v>91</v>
       </c>
-      <c r="M4" s="10">
-        <f t="shared" si="1"/>
-        <v>90</v>
-      </c>
-      <c r="N4" s="11">
+      <c r="N4" s="10">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="O4" s="11">
         <v>85</v>
       </c>
-      <c r="O4" s="12">
+      <c r="P4" s="12">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
     </row>
-    <row r="5" ht="16.35" customHeight="1" spans="1:15">
+    <row r="5" ht="16.35" customHeight="1" spans="1:16">
       <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>115</v>
+      <c r="B5" s="7">
+        <v>1</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G5" s="7">
         <v>96</v>
       </c>
-      <c r="G5" s="7">
+      <c r="H5" s="7">
         <v>93</v>
       </c>
-      <c r="H5" s="9">
+      <c r="I5" s="9">
         <v>96</v>
       </c>
-      <c r="I5" s="10">
+      <c r="J5" s="10">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="J5" s="10">
+      <c r="K5" s="10">
         <v>89</v>
       </c>
-      <c r="K5" s="10">
-        <v>90</v>
-      </c>
       <c r="L5" s="10">
+        <v>90</v>
+      </c>
+      <c r="M5" s="10">
         <v>89</v>
       </c>
-      <c r="M5" s="10">
+      <c r="N5" s="10">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="N5" s="11">
+      <c r="O5" s="11">
         <v>84</v>
       </c>
-      <c r="O5" s="12">
+      <c r="P5" s="12">
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
     </row>
-    <row r="6" ht="16.35" customHeight="1" spans="1:15">
+    <row r="6" ht="16.35" customHeight="1" spans="1:16">
       <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>117</v>
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6" s="7">
         <v>91</v>
       </c>
-      <c r="G6" s="7">
+      <c r="H6" s="7">
         <v>96</v>
       </c>
-      <c r="H6" s="9">
+      <c r="I6" s="9">
         <v>95</v>
       </c>
-      <c r="I6" s="10">
+      <c r="J6" s="10">
         <f t="shared" si="0"/>
         <v>94</v>
-      </c>
-      <c r="J6" s="10">
-        <v>88</v>
       </c>
       <c r="K6" s="10">
         <v>88</v>
       </c>
       <c r="L6" s="10">
+        <v>88</v>
+      </c>
+      <c r="M6" s="10">
         <v>87</v>
       </c>
-      <c r="M6" s="10">
+      <c r="N6" s="10">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="N6" s="11">
+      <c r="O6" s="11">
         <v>80</v>
       </c>
-      <c r="O6" s="12">
+      <c r="P6" s="12">
         <f t="shared" si="2"/>
         <v>85.5</v>
       </c>
     </row>
-    <row r="7" ht="16.35" customHeight="1" spans="1:15">
+    <row r="7" ht="16.35" customHeight="1" spans="1:16">
       <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>119</v>
+      <c r="B7" s="7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="G7" s="7">
         <v>66</v>
       </c>
-      <c r="G7" s="7">
+      <c r="H7" s="7">
         <v>97</v>
       </c>
-      <c r="H7" s="9">
+      <c r="I7" s="9">
         <v>94</v>
       </c>
-      <c r="I7" s="10">
+      <c r="J7" s="10">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
-      <c r="J7" s="10">
+      <c r="K7" s="10">
         <v>84</v>
       </c>
-      <c r="K7" s="10">
+      <c r="L7" s="10">
         <v>86</v>
       </c>
-      <c r="L7" s="10">
+      <c r="M7" s="10">
         <v>87</v>
       </c>
-      <c r="M7" s="10">
+      <c r="N7" s="10">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
-      <c r="N7" s="11">
+      <c r="O7" s="11">
         <v>68</v>
       </c>
-      <c r="O7" s="12">
+      <c r="P7" s="12">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
     </row>
-    <row r="8" ht="16.35" customHeight="1" spans="1:15">
+    <row r="8" ht="16.35" customHeight="1" spans="1:16">
       <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="E8" s="7" t="s">
+      <c r="B8" s="7">
+        <v>1</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="G8" s="7">
         <v>81</v>
       </c>
-      <c r="G8" s="7">
+      <c r="H8" s="7">
         <v>96</v>
       </c>
-      <c r="H8" s="9">
+      <c r="I8" s="9">
         <v>89</v>
       </c>
-      <c r="I8" s="10">
+      <c r="J8" s="10">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="J8" s="10">
-        <v>90</v>
-      </c>
       <c r="K8" s="10">
+        <v>90</v>
+      </c>
+      <c r="L8" s="10">
         <v>92</v>
       </c>
-      <c r="L8" s="10">
+      <c r="M8" s="10">
         <v>91</v>
       </c>
-      <c r="M8" s="10">
+      <c r="N8" s="10">
         <f t="shared" si="1"/>
         <v>91</v>
       </c>
-      <c r="N8" s="11">
+      <c r="O8" s="11">
         <v>85</v>
       </c>
-      <c r="O8" s="12">
+      <c r="P8" s="12">
         <f t="shared" si="2"/>
         <v>87.5</v>
       </c>
     </row>
-    <row r="9" ht="16.35" customHeight="1" spans="1:15">
+    <row r="9" ht="16.35" customHeight="1" spans="1:16">
       <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>123</v>
+      <c r="B9" s="7">
+        <v>1</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G9" s="7">
         <v>53</v>
       </c>
-      <c r="G9" s="7">
+      <c r="H9" s="7">
         <v>94</v>
       </c>
-      <c r="H9" s="9">
+      <c r="I9" s="9">
         <v>84</v>
       </c>
-      <c r="I9" s="10">
+      <c r="J9" s="10">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="J9" s="10">
+      <c r="K9" s="10">
         <v>91</v>
       </c>
-      <c r="K9" s="10">
+      <c r="L9" s="10">
         <v>88</v>
       </c>
-      <c r="L9" s="10">
+      <c r="M9" s="10">
         <v>89</v>
       </c>
-      <c r="M9" s="10">
+      <c r="N9" s="10">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="N9" s="11">
+      <c r="O9" s="11">
         <v>61</v>
       </c>
-      <c r="O9" s="12">
+      <c r="P9" s="12">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
     </row>
-    <row r="10" ht="16.35" customHeight="1" spans="1:15">
+    <row r="10" ht="16.35" customHeight="1" spans="1:16">
       <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>125</v>
+      <c r="B10" s="7">
+        <v>1</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" s="7">
         <v>72</v>
       </c>
-      <c r="G10" s="7">
+      <c r="H10" s="7">
         <v>91</v>
       </c>
-      <c r="H10" s="9">
+      <c r="I10" s="9">
         <v>88</v>
       </c>
-      <c r="I10" s="10">
+      <c r="J10" s="10">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="J10" s="10">
+      <c r="K10" s="10">
         <v>83</v>
       </c>
-      <c r="K10" s="10">
-        <v>90</v>
-      </c>
       <c r="L10" s="10">
         <v>90</v>
       </c>
       <c r="M10" s="10">
+        <v>90</v>
+      </c>
+      <c r="N10" s="10">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="N10" s="11">
+      <c r="O10" s="11">
         <v>79</v>
       </c>
-      <c r="O10" s="12">
+      <c r="P10" s="12">
         <f t="shared" si="2"/>
         <v>82.5</v>
       </c>
     </row>
-    <row r="11" ht="16.35" customHeight="1" spans="1:15">
+    <row r="11" ht="16.35" customHeight="1" spans="1:16">
       <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>127</v>
+      <c r="B11" s="7">
+        <v>1</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" s="7">
         <v>74</v>
       </c>
-      <c r="G11" s="7">
+      <c r="H11" s="7">
         <v>92</v>
       </c>
-      <c r="H11" s="9">
+      <c r="I11" s="9">
         <v>95</v>
       </c>
-      <c r="I11" s="10">
+      <c r="J11" s="10">
         <f t="shared" si="0"/>
         <v>87</v>
-      </c>
-      <c r="J11" s="10">
-        <v>89</v>
       </c>
       <c r="K11" s="10">
         <v>89</v>
       </c>
       <c r="L11" s="10">
+        <v>89</v>
+      </c>
+      <c r="M11" s="10">
         <v>88</v>
       </c>
-      <c r="M11" s="10">
+      <c r="N11" s="10">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="N11" s="11">
+      <c r="O11" s="11">
         <v>75</v>
       </c>
-      <c r="O11" s="12">
+      <c r="P11" s="12">
         <f t="shared" si="2"/>
         <v>81.5</v>
       </c>
     </row>
-    <row r="12" ht="16.35" customHeight="1" spans="1:15">
+    <row r="12" ht="16.35" customHeight="1" spans="1:16">
       <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>129</v>
+      <c r="B12" s="7">
+        <v>1</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="7">
         <v>86</v>
       </c>
-      <c r="G12" s="7">
+      <c r="H12" s="7">
         <v>92</v>
       </c>
-      <c r="H12" s="9">
+      <c r="I12" s="9">
         <v>87</v>
       </c>
-      <c r="I12" s="10">
+      <c r="J12" s="10">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="J12" s="10">
+      <c r="K12" s="10">
         <v>87</v>
       </c>
-      <c r="K12" s="10">
+      <c r="L12" s="10">
         <v>86</v>
       </c>
-      <c r="L12" s="10">
+      <c r="M12" s="10">
         <v>87</v>
       </c>
-      <c r="M12" s="10">
+      <c r="N12" s="10">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="N12" s="11">
+      <c r="O12" s="11">
         <v>82</v>
       </c>
-      <c r="O12" s="12">
+      <c r="P12" s="12">
         <f t="shared" si="2"/>
         <v>84.75</v>
       </c>
     </row>
-    <row r="13" ht="16.35" customHeight="1" spans="1:15">
+    <row r="13" ht="16.35" customHeight="1" spans="1:16">
       <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>131</v>
+      <c r="B13" s="7">
+        <v>1</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G13" s="7">
         <v>62</v>
       </c>
-      <c r="G13" s="7">
+      <c r="H13" s="7">
         <v>96</v>
       </c>
-      <c r="H13" s="9">
+      <c r="I13" s="9">
         <v>89</v>
       </c>
-      <c r="I13" s="10">
+      <c r="J13" s="10">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="J13" s="10">
+      <c r="K13" s="10">
         <v>95</v>
       </c>
-      <c r="K13" s="10">
-        <v>90</v>
-      </c>
       <c r="L13" s="10">
+        <v>90</v>
+      </c>
+      <c r="M13" s="10">
         <v>91</v>
       </c>
-      <c r="M13" s="10">
+      <c r="N13" s="10">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
-      <c r="N13" s="11">
+      <c r="O13" s="11">
         <v>78</v>
       </c>
-      <c r="O13" s="12">
+      <c r="P13" s="12">
         <f t="shared" si="2"/>
         <v>82.5</v>
       </c>
     </row>
-    <row r="14" ht="16.35" customHeight="1" spans="1:15">
+    <row r="14" ht="16.35" customHeight="1" spans="1:16">
       <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>133</v>
+      <c r="B14" s="7">
+        <v>1</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G14" s="7">
         <v>81</v>
       </c>
-      <c r="G14" s="7">
+      <c r="H14" s="7">
         <v>92</v>
       </c>
-      <c r="H14" s="9">
+      <c r="I14" s="9">
         <v>94</v>
       </c>
-      <c r="I14" s="10">
+      <c r="J14" s="10">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="J14" s="10">
+      <c r="K14" s="10">
         <v>84</v>
       </c>
-      <c r="K14" s="10">
+      <c r="L14" s="10">
         <v>88</v>
       </c>
-      <c r="L14" s="10">
+      <c r="M14" s="10">
         <v>87</v>
       </c>
-      <c r="M14" s="10">
+      <c r="N14" s="10">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
-      <c r="N14" s="11">
+      <c r="O14" s="11">
         <v>85</v>
       </c>
-      <c r="O14" s="12">
+      <c r="P14" s="12">
         <f t="shared" si="2"/>
         <v>86.25</v>
       </c>
     </row>
-    <row r="15" ht="16.35" customHeight="1" spans="1:15">
+    <row r="15" ht="16.35" customHeight="1" spans="1:16">
       <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>135</v>
+      <c r="B15" s="7">
+        <v>1</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="G15" s="7">
         <v>63</v>
       </c>
-      <c r="G15" s="7">
+      <c r="H15" s="7">
         <v>94</v>
       </c>
-      <c r="H15" s="9">
+      <c r="I15" s="9">
         <v>85</v>
       </c>
-      <c r="I15" s="10">
+      <c r="J15" s="10">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="J15" s="10">
+      <c r="K15" s="10">
         <v>83</v>
       </c>
-      <c r="K15" s="10">
-        <v>90</v>
-      </c>
       <c r="L15" s="10">
         <v>90</v>
       </c>
       <c r="M15" s="10">
+        <v>90</v>
+      </c>
+      <c r="N15" s="10">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="N15" s="11">
+      <c r="O15" s="11">
         <v>86</v>
       </c>
-      <c r="O15" s="12">
+      <c r="P15" s="12">
         <f t="shared" si="2"/>
         <v>85.25</v>
       </c>
     </row>
-    <row r="16" ht="16.35" customHeight="1" spans="1:15">
+    <row r="16" ht="16.35" customHeight="1" spans="1:16">
       <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>137</v>
+      <c r="B16" s="7">
+        <v>1</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G16" s="7">
         <v>85</v>
       </c>
-      <c r="G16" s="7">
+      <c r="H16" s="7">
         <v>96</v>
       </c>
-      <c r="H16" s="9">
+      <c r="I16" s="9">
         <v>91</v>
       </c>
-      <c r="I16" s="10">
+      <c r="J16" s="10">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="J16" s="10">
+      <c r="K16" s="10">
         <v>91</v>
       </c>
-      <c r="K16" s="10">
+      <c r="L16" s="10">
         <v>88</v>
       </c>
-      <c r="L16" s="10">
+      <c r="M16" s="10">
         <v>89</v>
       </c>
-      <c r="M16" s="10">
+      <c r="N16" s="10">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="N16" s="11">
+      <c r="O16" s="11">
         <v>81</v>
       </c>
-      <c r="O16" s="12">
+      <c r="P16" s="12">
         <f t="shared" si="2"/>
         <v>85.5</v>
       </c>
     </row>
-    <row r="17" ht="16.35" customHeight="1" spans="1:15">
+    <row r="17" ht="16.35" customHeight="1" spans="1:16">
       <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>139</v>
+      <c r="B17" s="7">
+        <v>1</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G17" s="7">
         <v>47</v>
       </c>
-      <c r="G17" s="7">
+      <c r="H17" s="7">
         <v>97</v>
       </c>
-      <c r="H17" s="9">
+      <c r="I17" s="9">
         <v>92</v>
       </c>
-      <c r="I17" s="10">
+      <c r="J17" s="10">
         <f t="shared" si="0"/>
         <v>79</v>
       </c>
-      <c r="J17" s="10">
+      <c r="K17" s="10">
         <v>84</v>
       </c>
-      <c r="K17" s="10">
-        <v>90</v>
-      </c>
       <c r="L17" s="10">
         <v>90</v>
       </c>
       <c r="M17" s="10">
+        <v>90</v>
+      </c>
+      <c r="N17" s="10">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="N17" s="11">
+      <c r="O17" s="11">
         <v>75</v>
       </c>
-      <c r="O17" s="12">
+      <c r="P17" s="12">
         <f t="shared" si="2"/>
         <v>79.25</v>
       </c>
     </row>
-    <row r="18" ht="16.35" customHeight="1" spans="1:15">
+    <row r="18" ht="16.35" customHeight="1" spans="1:16">
       <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>141</v>
+      <c r="B18" s="7">
+        <v>1</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G18" s="7">
         <v>95</v>
       </c>
-      <c r="G18" s="7">
+      <c r="H18" s="7">
         <v>97</v>
       </c>
-      <c r="H18" s="9">
+      <c r="I18" s="9">
         <v>94</v>
       </c>
-      <c r="I18" s="10">
+      <c r="J18" s="10">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="J18" s="10">
+      <c r="K18" s="10">
         <v>92</v>
       </c>
-      <c r="K18" s="10">
+      <c r="L18" s="10">
         <v>89</v>
       </c>
-      <c r="L18" s="10">
-        <v>90</v>
-      </c>
       <c r="M18" s="10">
-        <f t="shared" si="1"/>
-        <v>90</v>
-      </c>
-      <c r="N18" s="11">
+        <v>90</v>
+      </c>
+      <c r="N18" s="10">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="O18" s="11">
         <v>92</v>
       </c>
-      <c r="O18" s="12">
+      <c r="P18" s="12">
         <f t="shared" si="2"/>
         <v>92.25</v>
       </c>
     </row>
-    <row r="19" ht="16.35" customHeight="1" spans="1:15">
+    <row r="19" ht="16.35" customHeight="1" spans="1:16">
       <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>143</v>
+      <c r="B19" s="7">
+        <v>1</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="G19" s="7">
         <v>95</v>
       </c>
-      <c r="G19" s="7">
+      <c r="H19" s="7">
         <v>96</v>
       </c>
-      <c r="H19" s="9">
+      <c r="I19" s="9">
         <v>88</v>
       </c>
-      <c r="I19" s="10">
+      <c r="J19" s="10">
         <f t="shared" si="0"/>
         <v>93</v>
-      </c>
-      <c r="J19" s="10">
-        <v>89</v>
       </c>
       <c r="K19" s="10">
         <v>89</v>
@@ -4941,219 +5142,233 @@
         <v>89</v>
       </c>
       <c r="M19" s="10">
-        <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="N19" s="11">
+      <c r="N19" s="10">
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="O19" s="12">
-        <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" ht="16.35" customHeight="1" spans="1:15">
+      <c r="O19" s="11">
+        <v>89</v>
+      </c>
+      <c r="P19" s="12">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" ht="16.35" customHeight="1" spans="1:16">
       <c r="A20" s="7">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>145</v>
+      <c r="B20" s="7">
+        <v>1</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="F20" s="7">
-        <v>92</v>
+      <c r="F20" s="7" t="s">
+        <v>147</v>
       </c>
       <c r="G20" s="7">
         <v>92</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="7">
+        <v>92</v>
+      </c>
+      <c r="I20" s="9">
         <v>93</v>
       </c>
-      <c r="I20" s="10">
+      <c r="J20" s="10">
         <f t="shared" si="0"/>
         <v>92</v>
       </c>
-      <c r="J20" s="10">
-        <v>90</v>
-      </c>
       <c r="K20" s="10">
+        <v>90</v>
+      </c>
+      <c r="L20" s="10">
         <v>89</v>
       </c>
-      <c r="L20" s="10">
+      <c r="M20" s="10">
         <v>88</v>
       </c>
-      <c r="M20" s="10">
+      <c r="N20" s="10">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="N20" s="11">
+      <c r="O20" s="11">
         <v>92</v>
       </c>
-      <c r="O20" s="12">
+      <c r="P20" s="12">
         <f t="shared" si="2"/>
         <v>91.25</v>
       </c>
     </row>
-    <row r="21" ht="16.35" customHeight="1" spans="1:15">
+    <row r="21" ht="16.35" customHeight="1" spans="1:16">
       <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>147</v>
+      <c r="B21" s="7">
+        <v>1</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G21" s="7">
         <v>74</v>
       </c>
-      <c r="G21" s="7">
+      <c r="H21" s="7">
         <v>95</v>
       </c>
-      <c r="H21" s="9">
+      <c r="I21" s="9">
         <v>87</v>
       </c>
-      <c r="I21" s="10">
+      <c r="J21" s="10">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="J21" s="10">
+      <c r="K21" s="10">
         <v>85</v>
       </c>
-      <c r="K21" s="10">
+      <c r="L21" s="10">
         <v>87</v>
       </c>
-      <c r="L21" s="10">
+      <c r="M21" s="10">
         <v>88</v>
       </c>
-      <c r="M21" s="10">
+      <c r="N21" s="10">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="N21" s="11">
+      <c r="O21" s="11">
         <v>80</v>
       </c>
-      <c r="O21" s="12">
+      <c r="P21" s="12">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
     </row>
-    <row r="22" ht="16.35" customHeight="1" spans="1:15">
+    <row r="22" ht="16.35" customHeight="1" spans="1:16">
       <c r="A22" s="7">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>149</v>
+      <c r="B22" s="7">
+        <v>1</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G22" s="7">
         <v>52</v>
       </c>
-      <c r="G22" s="7">
-        <v>90</v>
-      </c>
-      <c r="H22" s="9">
+      <c r="H22" s="7">
+        <v>90</v>
+      </c>
+      <c r="I22" s="9">
         <v>77</v>
       </c>
-      <c r="I22" s="10">
+      <c r="J22" s="10">
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
-      <c r="J22" s="10">
+      <c r="K22" s="10">
         <v>82</v>
       </c>
-      <c r="K22" s="10">
+      <c r="L22" s="10">
         <v>85</v>
       </c>
-      <c r="L22" s="10">
+      <c r="M22" s="10">
         <v>87</v>
       </c>
-      <c r="M22" s="10">
+      <c r="N22" s="10">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
-      <c r="N22" s="11">
+      <c r="O22" s="11">
         <v>65</v>
       </c>
-      <c r="O22" s="12">
+      <c r="P22" s="12">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
     </row>
-    <row r="23" ht="16.35" customHeight="1" spans="1:15">
+    <row r="23" ht="16.35" customHeight="1" spans="1:16">
       <c r="A23" s="7">
         <v>22</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>151</v>
+      <c r="B23" s="7">
+        <v>1</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="G23" s="7">
         <v>73</v>
       </c>
-      <c r="G23" s="7">
+      <c r="H23" s="7">
         <v>97</v>
       </c>
-      <c r="H23" s="9">
+      <c r="I23" s="9">
         <v>94</v>
       </c>
-      <c r="I23" s="10">
+      <c r="J23" s="10">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="J23" s="10">
+      <c r="K23" s="10">
         <v>88</v>
       </c>
-      <c r="K23" s="10">
+      <c r="L23" s="10">
         <v>86</v>
       </c>
-      <c r="L23" s="10">
+      <c r="M23" s="10">
         <v>87</v>
       </c>
-      <c r="M23" s="10">
+      <c r="N23" s="10">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="N23" s="11">
+      <c r="O23" s="11">
         <v>80</v>
       </c>
-      <c r="O23" s="12">
+      <c r="P23" s="12">
         <f t="shared" si="2"/>
         <v>83.75</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
-      <c r="E24" s="13"/>
+    <row r="24" spans="1:16">
       <c r="F24" s="13"/>
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
@@ -5163,6 +5378,7 @@
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
       <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
